--- a/extenbooks/S1601_extenbook.xlsx
+++ b/extenbooks/S1601_extenbook.xlsx
@@ -25353,7 +25353,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -26839,11 +26839,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26866,76 +26866,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US and UK Golden Waves, 1786-2010</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension_deferred", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1601_research.json", "adequacy_report": "Technical/docs/chapters/CH16_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1601_DPR.md", "epr": "Technical/docs/series/S1601_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1601_load.py", "processor": "Technical/code/P02_processors/P02_S1601_construct.py", "validator": "Technical/code/V03_validators/V03_S1601_validate.py", "processed": "Technical/data/processed/S1601.parquet", "chopped_csv": "Technical/chopped/S1601.csv", "extenbook_xlsx": "Technical/extenbooks/S1601_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:17:23.977169+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1601_extenbook.xlsx
+++ b/extenbooks/S1601_extenbook.xlsx
@@ -25489,56 +25489,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
+          <t>The shipped chopped carries **four book-period subseries (A–D), all 1786-2010, all sourced from `SHAIKH_APPENDIX_5`** (registry `extension_deferred_to_phase6: true`):</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| **S1601-A** | 1786-2010 | Shaikh Appendix 5.3 — column `USGoldWaveDetrended` | deviation, 1930=100 | Salvaged xlsx (canonical book truth) |</t>
+          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| **S1601-B** | 1786-2010 | Shaikh Appendix 5.3 — column `UKGoldWaveDetrended` | deviation, 1930=100 | Salvaged xlsx (canonical book truth) |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| **S1601-C** | 2011-2024 | FRED `PPIACO` (BLS WPS00000000 mirror) for US WPI extension | Index 1982=100 | FRED API |</t>
+          <t>| **S1601-A** | 1786-2010 | Shaikh Appendix 5.3 — column `USGoldWaveDetrended` (US golden-wave residual) | deviation, 1930=100 | Salvaged xlsx (canonical book truth) |</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| **S1601-D** | 2011-2024 | FRED `GOLDPMGBD228NLBM` (LBMA Gold PM fix) for gold price extension | USD/oz | FRED API |</t>
+          <t>| **S1601-B** | 1786-2010 | Shaikh Appendix 5.3 — column `UKGoldWaveDetrended` (UK golden-wave residual) | deviation, 1930=100 | Salvaged xlsx (canonical book truth) |</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| **S1601-E** | 2011-2024 | ONS UK PPI K646 (output of manufactured products) for UK WPI extension | Index 2010=100 | ONS public CSV |</t>
+          <t>| **S1601-C** | 1786-2010 | Shaikh Appendix 5.3 — **US WPI / gold raw ratio** (`ratio_wpi_per_gold`), the cubic-trend **re-fit input** for S1601-A | ratio (WPI ÷ P_gold) | Salvaged xlsx (canonical book truth) |</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>| **S1601-F** | 1900-2024 | BoE Millennium dataset (UK historical WPI cross-check) | Index | Salvaged xlsx (cross-check only; not spliced) |</t>
+          <t>| **S1601-D** | 1786-2010 | Shaikh Appendix 5.3 — **UK WPI / gold raw ratio** (`ratio_wpi_per_gold`), the cubic-trend **re-fit input** for S1601-B | ratio (WPI ÷ P_gold) | Salvaged xlsx (canonical book truth) |</t>
         </is>
       </c>
     </row>
@@ -25548,7 +25544,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>The Phase 4 adequacy review verified all extension URLs return HTTP 200 and ratified BoE Millennium dataset as canonical UK historical successor to O'Donoghue/Goulding/Allen (2004).</t>
+          <t>**Extensions deferred to Phase 6 (NOT shipped).** The FRED `PPIACO` (US WPI), FRED `GOLDPMGBD228NLBM` (LBMA gold PM fix), ONS UK PPI `K646`, and BoE Millennium (UK historical WPI cross-check) splices that would carry S1601 to 2024 are declared in the registry as `extension_deferred_to_phase6: true` and are **absent from the shipped chopped** (book-period 1786-2010 only). An earlier draft of this DPR lettered those four extension sources as S1601-C/-D/-E/-F; that collided with the actual shipped C/D above (the 1786-2010 WPI/gold re-fit inputs). The deferred extension sources are documented in the EPR, not lettered here. (Corrected 2026-07-02, campaign DF-2.)</t>
         </is>
       </c>
     </row>
@@ -25588,7 +25584,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>**Extension variant (`refit_cubic_full_sample_1786_2024`)** — re-fits the cubic on the extended `WPI_t / P_gold_t` sample:</t>
+          <t>**Re-fit inputs shipped (`ratio_wpi_per_gold`)** — the raw `WPI_t / P_gold_t` ratios that feed the cubic re-fit are shipped as S1601-C (US) and S1601-D (UK) over the book period:</t>
         </is>
       </c>
     </row>
@@ -25602,14 +25598,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ln(USPPIGold_t)  ~  beta_0 + beta_1 * t + beta_2 * t^2 + beta_3 * t^3   (t = 1786..2024)</t>
+          <t>ln(WPIGold_t)    ~  beta_0 + beta_1 * t + beta_2 * t^2 + beta_3 * t^3   (t = 1786..2010)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>residual_t       =  ln(USPPIGold_t) - fitted_t</t>
+          <t>residual_t       =  ln(WPIGold_t) - fitted_t</t>
         </is>
       </c>
     </row>
@@ -25623,7 +25619,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S1601-A_extended =  100 * exp(dev_from_1930)</t>
+          <t>S1601-A          =  100 * exp(dev_from_1930)</t>
         </is>
       </c>
     </row>
@@ -25637,7 +25633,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Same procedure for UK. Both variants are emitted; the baseline is the "book-faithful" reference and the extended-sample re-fit is the modernised variant. Endpoint sensitivity is the documented structural fragility (see Caveats).</t>
+          <t>Same procedure for UK (S1601-B from S1601-D). The shipped chopped therefore contains BOTH the published cubic-trend residuals (A/B, book-faithful) AND the raw ratio inputs (C/D) that reproduce the book-period (1786-2010) re-fit. The **full-sample re-fit to 2024** (`refit_cubic_full_sample_1786_2024`) is **deferred to Phase 6** because it requires the deferred FRED/ONS/BoE extension splices; endpoint sensitivity is the documented structural fragility (see Caveats).</t>
         </is>
       </c>
     </row>
@@ -25657,21 +25653,21 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>- **Book period**: 1786-2010 (annual, 225 observations per country)</t>
+          <t>- **Book period**: 1786-2010 (annual, 225 observations per subseries; A–D each 225 obs)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>- **Extension period**: 2011-2024 (annual)</t>
+          <t>- **Extension period**: deferred to Phase 6 (2011-2024 FRED/ONS/BoE splices not yet shipped)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>- **Total coverage**: 1786-2024</t>
+          <t>- **Total coverage shipped**: 1786-2010</t>
         </is>
       </c>
     </row>
@@ -26824,7 +26820,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-19T00:19:54.117861+00:00</t>
+          <t>2026-07-02T06:20:00.223763+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1601_extenbook.xlsx
+++ b/extenbooks/S1601_extenbook.xlsx
@@ -26820,7 +26820,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T06:20:00.223763+00:00</t>
+          <t>2026-07-11T03:44:23.607947+00:00</t>
         </is>
       </c>
     </row>
@@ -26835,11 +26835,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26862,6 +26862,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "KB-verified: figure 16.1 caption, in-text description (p.727), and appendix 5.3 sourcing all match registry name, figures, and validation anchors; verbatim quotes confirmed.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1601_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1601_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Book-faithful pass-through of published cubic-trend residual columns; extended-sample re-fit emitted as Phase 6 variant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>deviation_from_cubic_trend_1930=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
